--- a/src/main/resources/be/vlaanderen/bodemenondergrond/data/id/conceptscheme/adertype/adertype.xlsx
+++ b/src/main/resources/be/vlaanderen/bodemenondergrond/data/id/conceptscheme/adertype/adertype.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:M34"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,784 +407,1395 @@
         <v>type</v>
       </c>
       <c r="C1" t="str">
+        <v>closeMatch</v>
+      </c>
+      <c r="D1" t="str">
+        <v>mappingRelation</v>
+      </c>
+      <c r="E1" t="str">
+        <v>semanticRelation</v>
+      </c>
+      <c r="F1" t="str">
         <v>dc\.identifier</v>
       </c>
-      <c r="D1" t="str">
+      <c r="G1" t="str">
+        <v>definition</v>
+      </c>
+      <c r="H1" t="str">
         <v>inScheme</v>
       </c>
-      <c r="E1" t="str">
-        <v>member</v>
-      </c>
-      <c r="F1" t="str">
+      <c r="I1" t="str">
         <v>notation</v>
       </c>
-      <c r="G1" t="str">
+      <c r="J1" t="str">
+        <v>note</v>
+      </c>
+      <c r="K1" t="str">
         <v>prefLabel</v>
       </c>
-      <c r="H1" t="str">
+      <c r="L1" t="str">
         <v>topConceptOf</v>
       </c>
-      <c r="I1" t="str">
+      <c r="M1" t="str">
         <v>hasTopConcept</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/collection/adertype/adertype</v>
+        <v>http://inspire.ec.europa.eu/codelist/CommodityCodeValue/calcite</v>
       </c>
       <c r="B2" t="str">
-        <v>http://www.w3.org/2004/02/skos/core#Collection</v>
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C2" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.collection.adertype.adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/CA</v>
       </c>
       <c r="D2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/CA</v>
       </c>
       <c r="E2" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/0|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/10|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/11|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/12|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/13|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/14|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/15|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/16|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/17|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/18|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/19|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/1|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/20|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/21|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/22|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/23|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/2|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/3|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/4|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/5|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/6|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/7|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/8|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/9</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/CA</v>
       </c>
       <c r="F2" t="str">
-        <v>collectie_adertypes</v>
+        <v>null</v>
       </c>
       <c r="G2" t="str">
-        <v>Collectie van adertype.</v>
+        <v>null</v>
       </c>
       <c r="H2" t="str">
         <v>null</v>
       </c>
       <c r="I2" t="str">
+        <v>null</v>
+      </c>
+      <c r="J2" t="str">
+        <v>null</v>
+      </c>
+      <c r="K2" t="str">
+        <v>null</v>
+      </c>
+      <c r="L2" t="str">
+        <v>null</v>
+      </c>
+      <c r="M2" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/0</v>
+        <v>http://inspire.ec.europa.eu/codelist/CommodityCodeValue/pyrite</v>
       </c>
       <c r="B3" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C3" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.0</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/PY</v>
       </c>
       <c r="D3" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/PY</v>
       </c>
       <c r="E3" t="str">
-        <v>null</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/PY</v>
       </c>
       <c r="F3" t="str">
-        <v>0</v>
+        <v>null</v>
       </c>
       <c r="G3" t="str">
-        <v>onbepaald</v>
+        <v>null</v>
       </c>
       <c r="H3" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>null</v>
       </c>
       <c r="I3" t="str">
+        <v>null</v>
+      </c>
+      <c r="J3" t="str">
+        <v>null</v>
+      </c>
+      <c r="K3" t="str">
+        <v>null</v>
+      </c>
+      <c r="L3" t="str">
+        <v>null</v>
+      </c>
+      <c r="M3" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/1</v>
+        <v>http://inspire.ec.europa.eu/codelist/CommodityCodeValue/quartz</v>
       </c>
       <c r="B4" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C4" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.1</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KD|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KO|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KW</v>
       </c>
       <c r="D4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KD|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KO|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KW</v>
       </c>
       <c r="E4" t="str">
-        <v>null</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KD|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KO|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KW</v>
       </c>
       <c r="F4" t="str">
-        <v>1</v>
+        <v>null</v>
       </c>
       <c r="G4" t="str">
-        <v>kaoliniet</v>
+        <v>null</v>
       </c>
       <c r="H4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>null</v>
       </c>
       <c r="I4" t="str">
+        <v>null</v>
+      </c>
+      <c r="J4" t="str">
+        <v>null</v>
+      </c>
+      <c r="K4" t="str">
+        <v>null</v>
+      </c>
+      <c r="L4" t="str">
+        <v>null</v>
+      </c>
+      <c r="M4" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/10</v>
+        <v>http://inspire.ec.europa.eu/codelist/LithologyValue/dolomite</v>
       </c>
       <c r="B5" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C5" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.10</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/DO</v>
       </c>
       <c r="D5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/DO</v>
       </c>
       <c r="E5" t="str">
-        <v>null</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/DO</v>
       </c>
       <c r="F5" t="str">
-        <v>10</v>
+        <v>null</v>
       </c>
       <c r="G5" t="str">
-        <v>galeniet</v>
+        <v>null</v>
       </c>
       <c r="H5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>null</v>
       </c>
       <c r="I5" t="str">
+        <v>null</v>
+      </c>
+      <c r="J5" t="str">
+        <v>null</v>
+      </c>
+      <c r="K5" t="str">
+        <v>null</v>
+      </c>
+      <c r="L5" t="str">
+        <v>null</v>
+      </c>
+      <c r="M5" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/11</v>
+        <v>http://inspire.ec.europa.eu/codelist/LithologyValue/gypsumOrAnhydrite</v>
       </c>
       <c r="B6" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C6" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.11</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/AN</v>
       </c>
       <c r="D6" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/AN</v>
       </c>
       <c r="E6" t="str">
-        <v>null</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/AN</v>
       </c>
       <c r="F6" t="str">
-        <v>11</v>
+        <v>null</v>
       </c>
       <c r="G6" t="str">
-        <v>pyriet</v>
+        <v>null</v>
       </c>
       <c r="H6" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>null</v>
       </c>
       <c r="I6" t="str">
+        <v>null</v>
+      </c>
+      <c r="J6" t="str">
+        <v>null</v>
+      </c>
+      <c r="K6" t="str">
+        <v>null</v>
+      </c>
+      <c r="L6" t="str">
+        <v>null</v>
+      </c>
+      <c r="M6" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/12</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/AN</v>
       </c>
       <c r="B7" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C7" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.12</v>
+        <v>http://inspire.ec.europa.eu/codelist/LithologyValue/gypsumOrAnhydrite</v>
       </c>
       <c r="D7" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>http://inspire.ec.europa.eu/codelist/LithologyValue/gypsumOrAnhydrite</v>
       </c>
       <c r="E7" t="str">
-        <v>null</v>
+        <v>http://inspire.ec.europa.eu/codelist/LithologyValue/gypsumOrAnhydrite</v>
       </c>
       <c r="F7" t="str">
-        <v>12</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.AN</v>
       </c>
       <c r="G7" t="str">
-        <v>calciet</v>
+        <v>Ader gevuld met anhydriet, de ongehydrateerde variant van het evaporitische mineraal gips.</v>
       </c>
       <c r="H7" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I7" t="str">
+        <v>AN</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Ader gevuld met anhydriet, de ongehydrateerde variant van het evaporitische mineraal gips.</v>
+      </c>
+      <c r="K7" t="str">
+        <v>anhydriet</v>
+      </c>
+      <c r="L7" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M7" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/13</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/BI</v>
       </c>
       <c r="B8" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C8" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.13</v>
+        <v>null</v>
       </c>
       <c r="D8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>null</v>
       </c>
       <c r="E8" t="str">
         <v>null</v>
       </c>
       <c r="F8" t="str">
-        <v>13</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.BI</v>
       </c>
       <c r="G8" t="str">
-        <v>dolomiet</v>
+        <v>Ader gevuld met materiaal een met verhoogd gehalte organische stof.</v>
       </c>
       <c r="H8" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I8" t="str">
+        <v>BI</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Ader gevuld met materiaal een met verhoogd gehalte organische stof.</v>
+      </c>
+      <c r="K8" t="str">
+        <v>kolig / bitumineus</v>
+      </c>
+      <c r="L8" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M8" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/14</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/BL</v>
       </c>
       <c r="B9" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C9" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.14</v>
+        <v>null</v>
       </c>
       <c r="D9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>null</v>
       </c>
       <c r="E9" t="str">
         <v>null</v>
       </c>
       <c r="F9" t="str">
-        <v>14</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.BL</v>
       </c>
       <c r="G9" t="str">
-        <v>hatchettiet</v>
+        <v>Ader gevuld met zinkblende (sfaleriet, zinksulfide).</v>
       </c>
       <c r="H9" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I9" t="str">
+        <v>BL</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Ader gevuld met zinkblende (sfaleriet, zinksulfide).</v>
+      </c>
+      <c r="K9" t="str">
+        <v>blende</v>
+      </c>
+      <c r="L9" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M9" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/15</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/BR</v>
       </c>
       <c r="B10" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C10" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.15</v>
+        <v>null</v>
       </c>
       <c r="D10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>null</v>
       </c>
       <c r="E10" t="str">
         <v>null</v>
       </c>
       <c r="F10" t="str">
-        <v>15</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.BR</v>
       </c>
       <c r="G10" t="str">
-        <v>kwarts</v>
+        <v>Ader gevuld met breccie, bestaande uit hoekige steenfragmenten in een fijnere matrix.</v>
       </c>
       <c r="H10" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I10" t="str">
+        <v>BR</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Ader gevuld met breccie, bestaande uit hoekige steenfragmenten in een fijnere matrix.</v>
+      </c>
+      <c r="K10" t="str">
+        <v>breccie</v>
+      </c>
+      <c r="L10" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M10" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/16</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/CA</v>
       </c>
       <c r="B11" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C11" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.16</v>
+        <v>http://inspire.ec.europa.eu/codelist/CommodityCodeValue/calcite</v>
       </c>
       <c r="D11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>http://inspire.ec.europa.eu/codelist/CommodityCodeValue/calcite</v>
       </c>
       <c r="E11" t="str">
-        <v>null</v>
+        <v>http://inspire.ec.europa.eu/codelist/CommodityCodeValue/calcite</v>
       </c>
       <c r="F11" t="str">
-        <v>16</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.CA</v>
       </c>
       <c r="G11" t="str">
-        <v>milleriet</v>
+        <v>Ader gevuld met calciet, kristallijn calciumcarbonaat.</v>
       </c>
       <c r="H11" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I11" t="str">
+        <v>CA</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Ader gevuld met calciet, kristallijn calciumcarbonaat.</v>
+      </c>
+      <c r="K11" t="str">
+        <v>calciet</v>
+      </c>
+      <c r="L11" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M11" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/17</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/CD</v>
       </c>
       <c r="B12" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C12" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.17</v>
+        <v>null</v>
       </c>
       <c r="D12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>null</v>
       </c>
       <c r="E12" t="str">
         <v>null</v>
       </c>
       <c r="F12" t="str">
-        <v>17</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.CD</v>
       </c>
       <c r="G12" t="str">
-        <v>gips</v>
+        <v>Ader gevuld met carbonaat, volledig dichtgegroeid.</v>
       </c>
       <c r="H12" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I12" t="str">
+        <v>CD</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Ader gevuld met carbonaat, volledig dichtgegroeid.</v>
+      </c>
+      <c r="K12" t="str">
+        <v>dicht met carbonaat</v>
+      </c>
+      <c r="L12" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M12" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/18</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/CH</v>
       </c>
       <c r="B13" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C13" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.18</v>
+        <v>null</v>
       </c>
       <c r="D13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>null</v>
       </c>
       <c r="E13" t="str">
         <v>null</v>
       </c>
       <c r="F13" t="str">
-        <v>18</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.CH</v>
       </c>
       <c r="G13" t="str">
-        <v>anhydriet</v>
+        <v>Ader gevuld met chalcopyriet (koperijzersulfide).</v>
       </c>
       <c r="H13" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I13" t="str">
+        <v>CH</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Ader gevuld met chalcopyriet (koperijzersulfide).</v>
+      </c>
+      <c r="K13" t="str">
+        <v>chalcopyriet</v>
+      </c>
+      <c r="L13" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M13" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/19</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/CO</v>
       </c>
       <c r="B14" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C14" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.19</v>
+        <v>null</v>
       </c>
       <c r="D14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>null</v>
       </c>
       <c r="E14" t="str">
         <v>null</v>
       </c>
       <c r="F14" t="str">
-        <v>19</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.CO</v>
       </c>
       <c r="G14" t="str">
-        <v>haliet</v>
+        <v>Ader deels gevuld met carbonaat, met open holtes.</v>
       </c>
       <c r="H14" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I14" t="str">
+        <v>CO</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Ader deels gevuld met carbonaat, met open holtes.</v>
+      </c>
+      <c r="K14" t="str">
+        <v>open met carbonaat</v>
+      </c>
+      <c r="L14" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M14" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/2</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/DO</v>
       </c>
       <c r="B15" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C15" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.2</v>
+        <v>http://inspire.ec.europa.eu/codelist/LithologyValue/dolomite</v>
       </c>
       <c r="D15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>http://inspire.ec.europa.eu/codelist/LithologyValue/dolomite</v>
       </c>
       <c r="E15" t="str">
-        <v>null</v>
+        <v>http://inspire.ec.europa.eu/codelist/LithologyValue/dolomite</v>
       </c>
       <c r="F15" t="str">
-        <v>2</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.DO</v>
       </c>
       <c r="G15" t="str">
-        <v>open met kwarts</v>
+        <v>Ader gevuld met dolomiet (calciummagnesiumcarbonaat).</v>
       </c>
       <c r="H15" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I15" t="str">
+        <v>DO</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Ader gevuld met dolomiet (calciummagnesiumcarbonaat).</v>
+      </c>
+      <c r="K15" t="str">
+        <v>dolomiet</v>
+      </c>
+      <c r="L15" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M15" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/20</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/GA</v>
       </c>
       <c r="B16" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C16" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.20</v>
+        <v>null</v>
       </c>
       <c r="D16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>null</v>
       </c>
       <c r="E16" t="str">
         <v>null</v>
       </c>
       <c r="F16" t="str">
-        <v>20</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.GA</v>
       </c>
       <c r="G16" t="str">
-        <v>mangaan</v>
+        <v>Ader gevuld met galeniet (loodsulfide).</v>
       </c>
       <c r="H16" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I16" t="str">
+        <v>GA</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Ader gevuld met galeniet (loodsulfide).</v>
+      </c>
+      <c r="K16" t="str">
+        <v>galeniet</v>
+      </c>
+      <c r="L16" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M16" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/21</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/GE</v>
       </c>
       <c r="B17" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C17" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.21</v>
+        <v>null</v>
       </c>
       <c r="D17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>null</v>
       </c>
       <c r="E17" t="str">
         <v>null</v>
       </c>
       <c r="F17" t="str">
-        <v>21</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.GE</v>
       </c>
       <c r="G17" t="str">
-        <v>klei (groen)</v>
+        <v>Ader gevuld met meerdere bestanddelen.</v>
       </c>
       <c r="H17" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I17" t="str">
+        <v>GE</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Ader gevuld met meerdere bestanddelen.</v>
+      </c>
+      <c r="K17" t="str">
+        <v>gemengd</v>
+      </c>
+      <c r="L17" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M17" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/22</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/GI</v>
       </c>
       <c r="B18" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C18" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.22</v>
+        <v>https://inspire.ec.europa.eu/codelist/CommodityCodeValue/gypsum</v>
       </c>
       <c r="D18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://inspire.ec.europa.eu/codelist/CommodityCodeValue/gypsum</v>
       </c>
       <c r="E18" t="str">
-        <v>null</v>
+        <v>https://inspire.ec.europa.eu/codelist/CommodityCodeValue/gypsum</v>
       </c>
       <c r="F18" t="str">
-        <v>22</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.GI</v>
       </c>
       <c r="G18" t="str">
-        <v>blinkend / kolig / bitumineus</v>
+        <v>Ader gevuld met gips (gehydrateerd calciumsulfaat).</v>
       </c>
       <c r="H18" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I18" t="str">
+        <v>GI</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Ader gevuld met gips (gehydrateerd calciumsulfaat).</v>
+      </c>
+      <c r="K18" t="str">
+        <v>gips</v>
+      </c>
+      <c r="L18" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M18" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/23</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/HA</v>
       </c>
       <c r="B19" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C19" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.23</v>
+        <v>https://inspire.ec.europa.eu/codelist/CommodityCodeValue/salt</v>
       </c>
       <c r="D19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://inspire.ec.europa.eu/codelist/CommodityCodeValue/salt</v>
       </c>
       <c r="E19" t="str">
-        <v>null</v>
+        <v>https://inspire.ec.europa.eu/codelist/CommodityCodeValue/salt</v>
       </c>
       <c r="F19" t="str">
-        <v>23</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.HA</v>
       </c>
       <c r="G19" t="str">
-        <v>chalcopyriet</v>
+        <v>Ader gevuld met haliet (steenzout, natriumchloride).</v>
       </c>
       <c r="H19" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I19" t="str">
+        <v>HA</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Ader gevuld met haliet (steenzout, natriumchloride).</v>
+      </c>
+      <c r="K19" t="str">
+        <v>haliet</v>
+      </c>
+      <c r="L19" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M19" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/3</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/HT</v>
       </c>
       <c r="B20" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C20" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.3</v>
+        <v>null</v>
       </c>
       <c r="D20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>null</v>
       </c>
       <c r="E20" t="str">
         <v>null</v>
       </c>
       <c r="F20" t="str">
-        <v>3</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.HT</v>
       </c>
       <c r="G20" t="str">
-        <v>dicht met kwarts</v>
+        <v>Ader gevuld met hatchettiet (mineraal koolwaterstof).</v>
       </c>
       <c r="H20" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I20" t="str">
+        <v>HT</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Ader gevuld met hatchettiet (mineraal koolwaterstof).</v>
+      </c>
+      <c r="K20" t="str">
+        <v>hatchettiet</v>
+      </c>
+      <c r="L20" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M20" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/4</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KA</v>
       </c>
       <c r="B21" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C21" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.4</v>
+        <v>https://inspire.ec.europa.eu/codelist/CommodityCodeValue/kaolin</v>
       </c>
       <c r="D21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://inspire.ec.europa.eu/codelist/CommodityCodeValue/kaolin</v>
       </c>
       <c r="E21" t="str">
-        <v>null</v>
+        <v>https://inspire.ec.europa.eu/codelist/CommodityCodeValue/kaolin</v>
       </c>
       <c r="F21" t="str">
-        <v>4</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.KA</v>
       </c>
       <c r="G21" t="str">
-        <v>open met carbonaat</v>
+        <v>Ader gevuld met kaoliniet, een verweerd wit kleimineraal.</v>
       </c>
       <c r="H21" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I21" t="str">
+        <v>KA</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Ader gevuld met kaoliniet, een verweerd wit kleimineraal.</v>
+      </c>
+      <c r="K21" t="str">
+        <v>kaoliniet</v>
+      </c>
+      <c r="L21" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M21" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/5</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KD</v>
       </c>
       <c r="B22" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C22" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.5</v>
+        <v>http://inspire.ec.europa.eu/codelist/CommodityCodeValue/quartz</v>
       </c>
       <c r="D22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>http://inspire.ec.europa.eu/codelist/CommodityCodeValue/quartz</v>
       </c>
       <c r="E22" t="str">
-        <v>null</v>
+        <v>http://inspire.ec.europa.eu/codelist/CommodityCodeValue/quartz</v>
       </c>
       <c r="F22" t="str">
-        <v>5</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.KD</v>
       </c>
       <c r="G22" t="str">
-        <v>dicht met carbonaat</v>
+        <v>Ader gevuld met kwarts (kristallijn siliciumdioxide), volledig dichtgegroeid.</v>
       </c>
       <c r="H22" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I22" t="str">
+        <v>KD</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Ader gevuld met kwarts (kristallijn siliciumdioxide), volledig dichtgegroeid.</v>
+      </c>
+      <c r="K22" t="str">
+        <v>dicht met kwarts</v>
+      </c>
+      <c r="L22" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M22" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/6</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KL</v>
       </c>
       <c r="B23" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C23" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.6</v>
+        <v>null</v>
       </c>
       <c r="D23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>null</v>
       </c>
       <c r="E23" t="str">
         <v>null</v>
       </c>
       <c r="F23" t="str">
-        <v>6</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.KL</v>
       </c>
       <c r="G23" t="str">
-        <v>sulfide</v>
+        <v>Ader gevuld met klei.</v>
       </c>
       <c r="H23" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I23" t="str">
+        <v>KL</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Ader gevuld met klei.</v>
+      </c>
+      <c r="K23" t="str">
+        <v>klei (groen)</v>
+      </c>
+      <c r="L23" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M23" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/7</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KO</v>
       </c>
       <c r="B24" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C24" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.7</v>
+        <v>http://inspire.ec.europa.eu/codelist/CommodityCodeValue/quartz</v>
       </c>
       <c r="D24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>http://inspire.ec.europa.eu/codelist/CommodityCodeValue/quartz</v>
       </c>
       <c r="E24" t="str">
-        <v>null</v>
+        <v>http://inspire.ec.europa.eu/codelist/CommodityCodeValue/quartz</v>
       </c>
       <c r="F24" t="str">
-        <v>7</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.KO</v>
       </c>
       <c r="G24" t="str">
-        <v>gemengd</v>
+        <v>Ader deels gevuld met kwarts (kristallijn siliciumdioxide), met open holtes.</v>
       </c>
       <c r="H24" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I24" t="str">
+        <v>KO</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Ader deels gevuld met kwarts (kristallijn siliciumdioxide), met open holtes.</v>
+      </c>
+      <c r="K24" t="str">
+        <v>open met kwarts</v>
+      </c>
+      <c r="L24" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M24" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/8</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KW</v>
       </c>
       <c r="B25" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C25" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.8</v>
+        <v>http://inspire.ec.europa.eu/codelist/CommodityCodeValue/quartz</v>
       </c>
       <c r="D25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>http://inspire.ec.europa.eu/codelist/CommodityCodeValue/quartz</v>
       </c>
       <c r="E25" t="str">
-        <v>null</v>
+        <v>http://inspire.ec.europa.eu/codelist/CommodityCodeValue/quartz</v>
       </c>
       <c r="F25" t="str">
-        <v>8</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.KW</v>
       </c>
       <c r="G25" t="str">
-        <v>breccie</v>
+        <v>Ader gevuld met kwarts (kristallijn siliciumdioxide).</v>
       </c>
       <c r="H25" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I25" t="str">
+        <v>KW</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Ader gevuld met kwarts (kristallijn siliciumdioxide).</v>
+      </c>
+      <c r="K25" t="str">
+        <v>kwarts</v>
+      </c>
+      <c r="L25" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M25" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/9</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/MA</v>
       </c>
       <c r="B26" t="str">
         <v>http://www.w3.org/2004/02/skos/core#Concept</v>
       </c>
       <c r="C26" t="str">
-        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.9</v>
+        <v>null</v>
       </c>
       <c r="D26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>null</v>
       </c>
       <c r="E26" t="str">
         <v>null</v>
       </c>
       <c r="F26" t="str">
-        <v>9</v>
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.MA</v>
       </c>
       <c r="G26" t="str">
-        <v>blende</v>
+        <v>Ader gevuld met mangaanmineralen.</v>
       </c>
       <c r="H26" t="str">
         <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I26" t="str">
+        <v>MA</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Ader gevuld met mangaanmineralen.</v>
+      </c>
+      <c r="K26" t="str">
+        <v>mangaan</v>
+      </c>
+      <c r="L26" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M26" t="str">
         <v>null</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/MI</v>
       </c>
       <c r="B27" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C27" t="str">
+        <v>null</v>
+      </c>
+      <c r="D27" t="str">
+        <v>null</v>
+      </c>
+      <c r="E27" t="str">
+        <v>null</v>
+      </c>
+      <c r="F27" t="str">
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.MI</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Ader gevuld met milleriet (nikkelsulfide).</v>
+      </c>
+      <c r="H27" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="I27" t="str">
+        <v>MI</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Ader gevuld met milleriet (nikkelsulfide).</v>
+      </c>
+      <c r="K27" t="str">
+        <v>milleriet</v>
+      </c>
+      <c r="L27" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M27" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/ON</v>
+      </c>
+      <c r="B28" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C28" t="str">
+        <v>null</v>
+      </c>
+      <c r="D28" t="str">
+        <v>null</v>
+      </c>
+      <c r="E28" t="str">
+        <v>null</v>
+      </c>
+      <c r="F28" t="str">
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.ON</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Ader gevuld met onbepaalde bestanddelen.</v>
+      </c>
+      <c r="H28" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="I28" t="str">
+        <v>ON</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Ader gevuld met onbepaalde bestanddelen.</v>
+      </c>
+      <c r="K28" t="str">
+        <v>onbepaald</v>
+      </c>
+      <c r="L28" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M28" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/PY</v>
+      </c>
+      <c r="B29" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C29" t="str">
+        <v>http://inspire.ec.europa.eu/codelist/CommodityCodeValue/pyrite</v>
+      </c>
+      <c r="D29" t="str">
+        <v>http://inspire.ec.europa.eu/codelist/CommodityCodeValue/pyrite</v>
+      </c>
+      <c r="E29" t="str">
+        <v>http://inspire.ec.europa.eu/codelist/CommodityCodeValue/pyrite</v>
+      </c>
+      <c r="F29" t="str">
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.PY</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Ader gevuld met pyriet (ijzersulfide).</v>
+      </c>
+      <c r="H29" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="I29" t="str">
+        <v>PY</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Ader gevuld met pyriet (ijzersulfide).</v>
+      </c>
+      <c r="K29" t="str">
+        <v>pyriet</v>
+      </c>
+      <c r="L29" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M29" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/SU</v>
+      </c>
+      <c r="B30" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C30" t="str">
+        <v>null</v>
+      </c>
+      <c r="D30" t="str">
+        <v>null</v>
+      </c>
+      <c r="E30" t="str">
+        <v>null</v>
+      </c>
+      <c r="F30" t="str">
+        <v>be.vlaanderen.bodemenondergrond.data.id.concept.adertype.SU</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Ader gevuld met sulfidemineralen.</v>
+      </c>
+      <c r="H30" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="I30" t="str">
+        <v>SU</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Ader gevuld met sulfidemineralen.</v>
+      </c>
+      <c r="K30" t="str">
+        <v>sulfide</v>
+      </c>
+      <c r="L30" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="M30" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+      </c>
+      <c r="B31" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
       </c>
-      <c r="C27" t="str">
+      <c r="C31" t="str">
+        <v>null</v>
+      </c>
+      <c r="D31" t="str">
+        <v>null</v>
+      </c>
+      <c r="E31" t="str">
+        <v>null</v>
+      </c>
+      <c r="F31" t="str">
         <v>be.vlaanderen.bodemenondergrond.data.id.conceptscheme.adertype</v>
       </c>
-      <c r="D27" t="str">
-        <v>null</v>
-      </c>
-      <c r="E27" t="str">
-        <v>null</v>
-      </c>
-      <c r="F27" t="str">
-        <v>adertypes</v>
-      </c>
-      <c r="G27" t="str">
-        <v>adertypes</v>
-      </c>
-      <c r="H27" t="str">
-        <v>null</v>
-      </c>
-      <c r="I27" t="str">
-        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/0|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/10|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/11|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/12|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/13|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/14|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/15|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/16|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/17|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/18|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/19|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/1|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/20|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/21|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/22|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/23|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/2|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/3|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/4|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/5|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/6|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/7|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/8|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/9</v>
+      <c r="G31" t="str">
+        <v>null</v>
+      </c>
+      <c r="H31" t="str">
+        <v>null</v>
+      </c>
+      <c r="I31" t="str">
+        <v>null</v>
+      </c>
+      <c r="J31" t="str">
+        <v>null</v>
+      </c>
+      <c r="K31" t="str">
+        <v>lijst met adertypes</v>
+      </c>
+      <c r="L31" t="str">
+        <v>null</v>
+      </c>
+      <c r="M31" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/CA|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/PY|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KD|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KO|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KW|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/DO|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/AN|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/BI|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/BL|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/BR|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/CD|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/CH|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/CO|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/GA|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/GE|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/GI|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/HA|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/HT|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KA|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KL|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/MA|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/MI|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/ON|https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/SU</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>https://inspire.ec.europa.eu/codelist/CommodityCodeValue/gypsum</v>
+      </c>
+      <c r="B32" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C32" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/GI</v>
+      </c>
+      <c r="D32" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/GI</v>
+      </c>
+      <c r="E32" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/GI</v>
+      </c>
+      <c r="F32" t="str">
+        <v>null</v>
+      </c>
+      <c r="G32" t="str">
+        <v>null</v>
+      </c>
+      <c r="H32" t="str">
+        <v>null</v>
+      </c>
+      <c r="I32" t="str">
+        <v>null</v>
+      </c>
+      <c r="J32" t="str">
+        <v>null</v>
+      </c>
+      <c r="K32" t="str">
+        <v>null</v>
+      </c>
+      <c r="L32" t="str">
+        <v>null</v>
+      </c>
+      <c r="M32" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>https://inspire.ec.europa.eu/codelist/CommodityCodeValue/kaolin</v>
+      </c>
+      <c r="B33" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C33" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KA</v>
+      </c>
+      <c r="D33" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KA</v>
+      </c>
+      <c r="E33" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/KA</v>
+      </c>
+      <c r="F33" t="str">
+        <v>null</v>
+      </c>
+      <c r="G33" t="str">
+        <v>null</v>
+      </c>
+      <c r="H33" t="str">
+        <v>null</v>
+      </c>
+      <c r="I33" t="str">
+        <v>null</v>
+      </c>
+      <c r="J33" t="str">
+        <v>null</v>
+      </c>
+      <c r="K33" t="str">
+        <v>null</v>
+      </c>
+      <c r="L33" t="str">
+        <v>null</v>
+      </c>
+      <c r="M33" t="str">
+        <v>null</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>https://inspire.ec.europa.eu/codelist/CommodityCodeValue/salt</v>
+      </c>
+      <c r="B34" t="str">
+        <v>http://www.w3.org/2004/02/skos/core#Concept</v>
+      </c>
+      <c r="C34" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/HA</v>
+      </c>
+      <c r="D34" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/HA</v>
+      </c>
+      <c r="E34" t="str">
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/concept/adertype/HA</v>
+      </c>
+      <c r="F34" t="str">
+        <v>null</v>
+      </c>
+      <c r="G34" t="str">
+        <v>null</v>
+      </c>
+      <c r="H34" t="str">
+        <v>null</v>
+      </c>
+      <c r="I34" t="str">
+        <v>null</v>
+      </c>
+      <c r="J34" t="str">
+        <v>null</v>
+      </c>
+      <c r="K34" t="str">
+        <v>null</v>
+      </c>
+      <c r="L34" t="str">
+        <v>null</v>
+      </c>
+      <c r="M34" t="str">
+        <v>null</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M34"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/main/resources/be/vlaanderen/bodemenondergrond/data/id/conceptscheme/adertype/adertype.xlsx
+++ b/src/main/resources/be/vlaanderen/bodemenondergrond/data/id/conceptscheme/adertype/adertype.xlsx
@@ -668,7 +668,7 @@
         <v>Ader gevuld met anhydriet, de ongehydrateerde variant van het evaporitische mineraal gips.</v>
       </c>
       <c r="H7" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I7" t="str">
         <v>AN</v>
@@ -680,7 +680,7 @@
         <v>anhydriet</v>
       </c>
       <c r="L7" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M7" t="str">
         <v>null</v>
@@ -709,7 +709,7 @@
         <v>Ader gevuld met materiaal een met verhoogd gehalte organische stof.</v>
       </c>
       <c r="H8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I8" t="str">
         <v>BI</v>
@@ -721,7 +721,7 @@
         <v>kolig / bitumineus</v>
       </c>
       <c r="L8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M8" t="str">
         <v>null</v>
@@ -750,7 +750,7 @@
         <v>Ader gevuld met zinkblende (sfaleriet, zinksulfide).</v>
       </c>
       <c r="H9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I9" t="str">
         <v>BL</v>
@@ -762,7 +762,7 @@
         <v>blende</v>
       </c>
       <c r="L9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M9" t="str">
         <v>null</v>
@@ -791,7 +791,7 @@
         <v>Ader gevuld met breccie, bestaande uit hoekige steenfragmenten in een fijnere matrix.</v>
       </c>
       <c r="H10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I10" t="str">
         <v>BR</v>
@@ -803,7 +803,7 @@
         <v>breccie</v>
       </c>
       <c r="L10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M10" t="str">
         <v>null</v>
@@ -832,7 +832,7 @@
         <v>Ader gevuld met calciet, kristallijn calciumcarbonaat.</v>
       </c>
       <c r="H11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I11" t="str">
         <v>CA</v>
@@ -844,7 +844,7 @@
         <v>calciet</v>
       </c>
       <c r="L11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M11" t="str">
         <v>null</v>
@@ -873,7 +873,7 @@
         <v>Ader gevuld met carbonaat, volledig dichtgegroeid.</v>
       </c>
       <c r="H12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I12" t="str">
         <v>CD</v>
@@ -885,7 +885,7 @@
         <v>dicht met carbonaat</v>
       </c>
       <c r="L12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M12" t="str">
         <v>null</v>
@@ -914,7 +914,7 @@
         <v>Ader gevuld met chalcopyriet (koperijzersulfide).</v>
       </c>
       <c r="H13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I13" t="str">
         <v>CH</v>
@@ -926,7 +926,7 @@
         <v>chalcopyriet</v>
       </c>
       <c r="L13" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M13" t="str">
         <v>null</v>
@@ -955,7 +955,7 @@
         <v>Ader deels gevuld met carbonaat, met open holtes.</v>
       </c>
       <c r="H14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I14" t="str">
         <v>CO</v>
@@ -967,7 +967,7 @@
         <v>open met carbonaat</v>
       </c>
       <c r="L14" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M14" t="str">
         <v>null</v>
@@ -996,7 +996,7 @@
         <v>Ader gevuld met dolomiet (calciummagnesiumcarbonaat).</v>
       </c>
       <c r="H15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I15" t="str">
         <v>DO</v>
@@ -1008,7 +1008,7 @@
         <v>dolomiet</v>
       </c>
       <c r="L15" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M15" t="str">
         <v>null</v>
@@ -1037,7 +1037,7 @@
         <v>Ader gevuld met galeniet (loodsulfide).</v>
       </c>
       <c r="H16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I16" t="str">
         <v>GA</v>
@@ -1049,7 +1049,7 @@
         <v>galeniet</v>
       </c>
       <c r="L16" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M16" t="str">
         <v>null</v>
@@ -1078,7 +1078,7 @@
         <v>Ader gevuld met meerdere bestanddelen.</v>
       </c>
       <c r="H17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I17" t="str">
         <v>GE</v>
@@ -1090,7 +1090,7 @@
         <v>gemengd</v>
       </c>
       <c r="L17" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M17" t="str">
         <v>null</v>
@@ -1119,7 +1119,7 @@
         <v>Ader gevuld met gips (gehydrateerd calciumsulfaat).</v>
       </c>
       <c r="H18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I18" t="str">
         <v>GI</v>
@@ -1131,7 +1131,7 @@
         <v>gips</v>
       </c>
       <c r="L18" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M18" t="str">
         <v>null</v>
@@ -1160,7 +1160,7 @@
         <v>Ader gevuld met haliet (steenzout, natriumchloride).</v>
       </c>
       <c r="H19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I19" t="str">
         <v>HA</v>
@@ -1172,7 +1172,7 @@
         <v>haliet</v>
       </c>
       <c r="L19" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M19" t="str">
         <v>null</v>
@@ -1201,7 +1201,7 @@
         <v>Ader gevuld met hatchettiet (mineraal koolwaterstof).</v>
       </c>
       <c r="H20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I20" t="str">
         <v>HT</v>
@@ -1213,7 +1213,7 @@
         <v>hatchettiet</v>
       </c>
       <c r="L20" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M20" t="str">
         <v>null</v>
@@ -1242,7 +1242,7 @@
         <v>Ader gevuld met kaoliniet, een verweerd wit kleimineraal.</v>
       </c>
       <c r="H21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I21" t="str">
         <v>KA</v>
@@ -1254,7 +1254,7 @@
         <v>kaoliniet</v>
       </c>
       <c r="L21" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M21" t="str">
         <v>null</v>
@@ -1283,7 +1283,7 @@
         <v>Ader gevuld met kwarts (kristallijn siliciumdioxide), volledig dichtgegroeid.</v>
       </c>
       <c r="H22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I22" t="str">
         <v>KD</v>
@@ -1295,7 +1295,7 @@
         <v>dicht met kwarts</v>
       </c>
       <c r="L22" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M22" t="str">
         <v>null</v>
@@ -1324,7 +1324,7 @@
         <v>Ader gevuld met klei.</v>
       </c>
       <c r="H23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I23" t="str">
         <v>KL</v>
@@ -1336,7 +1336,7 @@
         <v>klei (groen)</v>
       </c>
       <c r="L23" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M23" t="str">
         <v>null</v>
@@ -1365,7 +1365,7 @@
         <v>Ader deels gevuld met kwarts (kristallijn siliciumdioxide), met open holtes.</v>
       </c>
       <c r="H24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I24" t="str">
         <v>KO</v>
@@ -1377,7 +1377,7 @@
         <v>open met kwarts</v>
       </c>
       <c r="L24" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M24" t="str">
         <v>null</v>
@@ -1406,7 +1406,7 @@
         <v>Ader gevuld met kwarts (kristallijn siliciumdioxide).</v>
       </c>
       <c r="H25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I25" t="str">
         <v>KW</v>
@@ -1418,7 +1418,7 @@
         <v>kwarts</v>
       </c>
       <c r="L25" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M25" t="str">
         <v>null</v>
@@ -1447,7 +1447,7 @@
         <v>Ader gevuld met mangaanmineralen.</v>
       </c>
       <c r="H26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I26" t="str">
         <v>MA</v>
@@ -1459,7 +1459,7 @@
         <v>mangaan</v>
       </c>
       <c r="L26" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M26" t="str">
         <v>null</v>
@@ -1488,7 +1488,7 @@
         <v>Ader gevuld met milleriet (nikkelsulfide).</v>
       </c>
       <c r="H27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I27" t="str">
         <v>MI</v>
@@ -1500,7 +1500,7 @@
         <v>milleriet</v>
       </c>
       <c r="L27" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M27" t="str">
         <v>null</v>
@@ -1529,7 +1529,7 @@
         <v>Ader gevuld met onbepaalde bestanddelen.</v>
       </c>
       <c r="H28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I28" t="str">
         <v>ON</v>
@@ -1541,7 +1541,7 @@
         <v>onbepaald</v>
       </c>
       <c r="L28" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M28" t="str">
         <v>null</v>
@@ -1570,7 +1570,7 @@
         <v>Ader gevuld met pyriet (ijzersulfide).</v>
       </c>
       <c r="H29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I29" t="str">
         <v>PY</v>
@@ -1582,7 +1582,7 @@
         <v>pyriet</v>
       </c>
       <c r="L29" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M29" t="str">
         <v>null</v>
@@ -1611,7 +1611,7 @@
         <v>Ader gevuld met sulfidemineralen.</v>
       </c>
       <c r="H30" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="I30" t="str">
         <v>SU</v>
@@ -1623,7 +1623,7 @@
         <v>sulfide</v>
       </c>
       <c r="L30" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="M30" t="str">
         <v>null</v>
@@ -1631,7 +1631,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/adertype</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/adertype</v>
       </c>
       <c r="B31" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
